--- a/光伏配储项目/电价数据/2026/榭平岭站.xlsx
+++ b/光伏配储项目/电价数据/2026/榭平岭站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72157</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56475</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51702</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45394</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45467</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26804</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21506</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25891</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07729000000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06344</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05183</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03245</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05364</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04501</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.00895</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01667</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08623</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01579</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00105</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00357</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14524</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21299</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23617</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21414</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11602</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00398</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00687</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.1565</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.27118</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.19154</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22354</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.19913</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12311</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19474</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.26612</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.00492</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.23616</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.00226</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44944</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.48253</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.76201</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6148899999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.5107699999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.50862</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.12932</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.58648</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.54171</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.26381</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.49991</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50306</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6145</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.57077</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43318</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48979</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42762</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43838</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6232300000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.42895</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7563799999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.17565</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8706499999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54562</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5275700000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5076499999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5153300000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.51114</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47725</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42534</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52807</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65435</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.75163</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44268</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08823</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04667</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25702</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.58954</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.20776</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27653</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.58204</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.01963</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26837</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.22992</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15875</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23261</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.25823</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.26011</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27202</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42273</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.26558</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.47033</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70847</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.92659</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.8814299999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.26795</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8458600000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.42852</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.82382</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4382200000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59842</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.35537</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5439299999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47389</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.44554</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40257</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.46232</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47401</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44289</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.16383</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.46512</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.60765</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.52612</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.44092</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.50439</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48688</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.06965</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21571</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.14718</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20538</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.1927</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24777</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.24643</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.21399</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.47767</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.02026</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.28717</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34408</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.27146</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27487</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47875</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27487</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26237</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26391</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19376</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10809</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11148</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08129</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.2507</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21256</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13034</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44802</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21237</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.0464</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06117</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17637</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04112</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.01062</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21306</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00144</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03066</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.04776</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07681</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.20308</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16694</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20376</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15225</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19664</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14269</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.20073</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22791</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25728</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28658</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47031</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25603</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29215</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27406</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27683</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04072</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04515</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04026</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04001</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04269</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04505</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04354</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04556</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04629999999999999</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.0471</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04788000000000001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04636999999999999</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04671</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04755</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04676</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04578</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04644</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.0479</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04872</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04729</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22003</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04646</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04895</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05171</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00214</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14707</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03756</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09884999999999999</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6644</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04591</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04511</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04401</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04183</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03234</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04069</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10693</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00106</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03742</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04111</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04128</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04119</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04357</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04109</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0405</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04329</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04035</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03897999999999999</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04402</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04373</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04109</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03997999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04266</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04306</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04644</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04603</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20234</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27138</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33774</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32289</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27366</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17435</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16061</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17324</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14959</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16069</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23959</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21611</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22871</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27199</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27084</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.5548500000000001</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.47589</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.53407</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.7619</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.52027</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.51403</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.47244</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.44199</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7910900000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9200199999999999</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92796</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.9065800000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31931</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.92971</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63875</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22856</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88932</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.58038</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37338</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06211</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5734600000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.82723</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.80944</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80644</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.88126</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.89291</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5272</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43192</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44361</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48881</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25071</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.88006</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55177</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.66523</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5491200000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.51017</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46113</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42938</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44481</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45201</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45325</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41367</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5896699999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59685</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60199</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64503</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.48925</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.7512799999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44737</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8650099999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.06158</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.01006</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.99414</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.92855</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.41911</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.5954299999999999</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.54373</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27327</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35329</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02459</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.49934</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.61888</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6931799999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.44942</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5105</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44761</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16473</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26108</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20117</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.6918800000000001</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27592</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.42834</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24961</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42825</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24624</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44702</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59766</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88976</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35741</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13663</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71173</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80574</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6513</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59085</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45102</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50043</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1.19973</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.47378</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.43921</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.45432</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.25344</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.87773</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.46606</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.03352</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.31174</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23774</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.85609</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.08197</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.45171</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26853</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.59993</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.44902</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48583</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.6073099999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46571</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.68509</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46671</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43959</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32652</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42571</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.49585</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.50888</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.27575</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23718</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14649</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14917</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15612</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14479</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14232</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14484</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14375</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25893</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14546</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26865</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26878</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14333</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05272</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11479</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11372</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14755</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14253</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14778</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28874</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45141</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43788</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4418</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44124</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44619</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44546</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35069</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.66037</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47034</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.42757</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.85349</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.5861799999999999</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.59253</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.58794</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.57773</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.48638</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.5406299999999999</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.5656599999999999</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.6273</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.4856</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.61495</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.61126</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.54911</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44635</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45921</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.5121599999999999</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36064</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28454</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.50428</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.51779</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.52261</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26981</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.41069</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03317000000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25448</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2101</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07499</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18436</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24496</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27109</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25314</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27452</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42811</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50573</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7773600000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45061</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46848</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30997</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.57321</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.59617</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28261</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35029</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.59981</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.73339</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41558</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6495700000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87621</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48711</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.48501</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46041</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39417</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34507</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26145</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13624</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19529</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24639</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.02683</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13054</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23755</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24788</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.00818</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14505</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.02326</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23384</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23669</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63366</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6035199999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.57897</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46226</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.58857</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47789</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.72942</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.4538</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48172</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49338</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46649</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45745</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4074700000000001</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41397</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45082</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5613400000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45097</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41513</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.45777</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.49376</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.54544</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15283</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04093</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03308</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.6527200000000001</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.20053</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.21612</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10685</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.00732</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26904</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03541</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48605</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50843</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.5774900000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.66176</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.64532</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.61958</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.68311</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5081600000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.49763</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7499400000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.69509</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.56811</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.60997</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46422</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46118</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45453</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50929</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43208</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44533</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42701</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44304</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44647</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39457</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27862</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15826</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27247</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03764</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45302</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46399</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01533</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18513</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36277</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44378</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.46312</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.48181</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24814</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23544</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23714</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25187</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03843</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.22269</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05521</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17551</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25936</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.03843</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14851</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15243</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05795</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.008029999999999999</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.39891</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.45559</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.54852</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.6019800000000001</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.5410700000000001</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.46641</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35496</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19359</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13172</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.15078</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04554</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00152</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04363</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.0415</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.03805</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.11641</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.1397</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19164</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27686</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22378</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22444</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22528</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.22954</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.23993</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26668</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24954</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24294</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.25015</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.2538</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25495</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24353</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24887</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27664</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.25921</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21893</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23905</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21712</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18712</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.08701</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.03586</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.24309</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.04309</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15708</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15741</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.02674</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23445</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21756</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.20242</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16649</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15822</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13384</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15807</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.1894</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.11097</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12521</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.19188</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.16166</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.21145</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.1844</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.22235</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.22262</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22944</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.21127</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21786</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.13237</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04117</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.20127</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.00158</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.17229</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16831</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02205</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18752</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26693</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.02461</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.08256000000000001</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.04499</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25226</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28172</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.19471</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32624</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10573</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.26932</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.41917</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25729</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.11814</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24254</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.5006499999999999</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2318</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25629</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.18861</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.1435</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10449</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33212</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.2414</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.73517</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.72185</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25388</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27316</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28337</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28137</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.17141</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26106</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26578</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26609</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26283</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24698</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28194</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.50774</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.53938</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.45142</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.48464</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.52876</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.52232</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.70177</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.69084</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.52059</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.05167</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.43208</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46907</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.54476</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47601</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45383</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43109</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.8645700000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.49783</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.44905</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46743</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.45811</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.20701</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23429</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26043</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19261</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26454</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27518</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.46691</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46567</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56003</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56129</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46193</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5516799999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46462</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49717</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5327000000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52049</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7074400000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.75264</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54991</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5525599999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39102</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37682</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27248</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29132</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27228</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26911</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26797</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26364</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25618</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24933</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.23903</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23767</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25476</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.19072</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13264</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.00735</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.04639</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.22213</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01207</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02435</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.00231</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01346</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02309</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.02719</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23529</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01691</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02143</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03133</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02198</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01412</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01774</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10515</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06334000000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11932</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13688</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16452</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22348</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18139</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18441</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20814</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.25088</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40475</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38065</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7403</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28478</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27682</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27165</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26123</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23301</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22663</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19571</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19571</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21645</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.15549</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.02731</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.02476</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.02419</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03616</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07883</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.08527</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00439</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04437</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.03425</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.03401</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.04076</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15561</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.07063</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.26036</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.25203</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.18703</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.27499</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.21909</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22461</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18351</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23623</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.52796</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40846</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43149</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38613</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.51227</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39579</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27231</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23255</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18759</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17262</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11309</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14878</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17529</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.16281</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08777</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10489</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07048</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03614</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03695</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03757</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05186</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05991</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03488</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05685</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07208000000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11501</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.1435</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08672000000000001</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.1641</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14543</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08962000000000001</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04618</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21498</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09619</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09151000000000001</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18751</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.13066</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.14093</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16735</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14681</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.18157</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.2006</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.20162</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21443</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25532</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25926</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49748</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41821</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44291</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38223</v>
       </c>
     </row>
   </sheetData>
